--- a/data/trans_camb/P1428-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1428-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,15</t>
+          <t>-1,58; 0,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; -0,21</t>
+          <t>-1,86; -0,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; -0,17</t>
+          <t>-1,76; -0,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,2</t>
+          <t>-0,62; 1,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,01</t>
+          <t>-0,75; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,54</t>
+          <t>-0,04; 5,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,34</t>
+          <t>-0,82; 0,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,17</t>
+          <t>-0,95; 0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,32</t>
+          <t>-0,47; 2,21</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>446,58%</t>
+          <t>429,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,16</t>
+          <t>-100,0; 208,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 132,04</t>
+          <t>-100,0; 128,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 744,83</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,1</t>
+          <t>-0,12; 2,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,62</t>
+          <t>-0,73; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; -0,14</t>
+          <t>-1,17; -0,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,18</t>
+          <t>-2,02; 0,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,24</t>
+          <t>-2,15; 0,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,16</t>
+          <t>-1,4; 1,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,94</t>
+          <t>-0,61; 0,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,26</t>
+          <t>-1,12; 0,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,55</t>
+          <t>-0,91; 0,55</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,34%</t>
+          <t>-2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,88%</t>
+          <t>-22,76%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 1467,84</t>
+          <t>-76,09; 1128,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-93,23; 69,99</t>
+          <t>-100,0; 90,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,29</t>
+          <t>-100,0; 110,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,51; 200,63</t>
+          <t>-73,21; 231,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,48; 199,66</t>
+          <t>-55,41; 174,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 86,42</t>
+          <t>-88,96; 70,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 173,8</t>
+          <t>-77,38; 116,25</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,8</t>
+          <t>-2,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>-1,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,34</t>
+          <t>-0,53; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,57</t>
+          <t>-0,48; 1,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,81</t>
+          <t>-0,51; 1,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -1,67</t>
+          <t>-5,97; -1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -2,66</t>
+          <t>-6,46; -2,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -0,69</t>
+          <t>-4,99; -0,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,62</t>
+          <t>-2,83; -0,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,86</t>
+          <t>-3,19; -0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,06</t>
+          <t>-2,5; -0,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-49,69%</t>
+          <t>-49,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-38,42%</t>
+          <t>-38,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 634,61</t>
+          <t>-65,85; 575,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 560,0</t>
+          <t>-67,13; 752,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 611,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,14; -33,05</t>
+          <t>-83,33; -36,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,47; -50,06</t>
+          <t>-91,01; -52,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,22; -12,93</t>
+          <t>-71,4; -11,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,12; -23,27</t>
+          <t>-72,14; -20,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,48; -31,42</t>
+          <t>-79,8; -30,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 0,66</t>
+          <t>-62,95; -1,42</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-1,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-5,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,13</t>
+          <t>-3,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -0,81</t>
+          <t>-5,41; -0,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,44</t>
+          <t>-3,43; 1,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,7</t>
+          <t>-3,57; 1,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -3,12</t>
+          <t>-10,74; -2,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -4,34</t>
+          <t>-11,82; -4,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -2,13</t>
+          <t>-9,42; -2,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,78</t>
+          <t>-7,17; -2,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -2,31</t>
+          <t>-6,94; -2,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; -2,05</t>
+          <t>-5,86; -1,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-39,32%</t>
+          <t>-22,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-39,3%</t>
+          <t>-41,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-42,6%</t>
+          <t>-35,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,23; -16,97</t>
+          <t>-82,82; -14,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,88; 45,45</t>
+          <t>-56,28; 44,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 14,11</t>
+          <t>-56,02; 34,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-63,07; -22,6</t>
+          <t>-63,36; -21,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,5; -34,06</t>
+          <t>-68,88; -35,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,52; -16,53</t>
+          <t>-54,61; -18,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,29; -30,53</t>
+          <t>-64,49; -31,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,13; -26,15</t>
+          <t>-62,79; -27,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -24,03</t>
+          <t>-51,27; -16,39</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-8,61</t>
+          <t>-9,01</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,55</t>
+          <t>-9,79</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-9,29</t>
+          <t>-9,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -2,26</t>
+          <t>-11,72; -2,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -7,67</t>
+          <t>-15,54; -6,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,73; -4,16</t>
+          <t>-13,73; -5,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -1,88</t>
+          <t>-13,9; -1,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,03; -6,23</t>
+          <t>-17,61; -6,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -4,32</t>
+          <t>-15,0; -5,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -3,79</t>
+          <t>-11,44; -3,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,4; -7,89</t>
+          <t>-15,21; -8,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -5,79</t>
+          <t>-13,04; -6,17</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-52,39%</t>
+          <t>-54,81%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-34,07%</t>
+          <t>-34,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,53%</t>
+          <t>-42,66%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,64; -13,26</t>
+          <t>-61,8; -15,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -51,4</t>
+          <t>-81,69; -48,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,42; -32,59</t>
+          <t>-68,26; -35,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,1; -8,06</t>
+          <t>-43,92; -7,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,78; -24,1</t>
+          <t>-56,23; -26,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,41; -18,05</t>
+          <t>-47,28; -20,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -18,67</t>
+          <t>-46,89; -18,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-62,52; -39,42</t>
+          <t>-62,09; -40,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,12; -28,55</t>
+          <t>-52,06; -31,67</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-11,47</t>
+          <t>-11,66</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>-16,8</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>-14,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 0,81</t>
+          <t>-12,21; 1,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -9,0</t>
+          <t>-20,62; -9,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,49; -6,15</t>
+          <t>-17,07; -6,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -6,47</t>
+          <t>-21,39; -7,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-28,27; -14,71</t>
+          <t>-29,07; -15,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 34,99</t>
+          <t>-22,93; -10,69</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -5,22</t>
+          <t>-15,23; -5,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-23,57; -14,51</t>
+          <t>-23,96; -14,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 32,61</t>
+          <t>-19,06; -10,5</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-52,28%</t>
+          <t>-53,15%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>-35,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>-41,82%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 5,94</t>
+          <t>-48,22; 10,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,24; -47,03</t>
+          <t>-79,6; -47,62</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-65,13; -34,21</t>
+          <t>-65,71; -33,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-42,74; -15,0</t>
+          <t>-43,13; -17,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-56,8; -33,71</t>
+          <t>-57,71; -34,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 78,09</t>
+          <t>-44,35; -25,32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -15,84</t>
+          <t>-40,31; -16,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-62,08; -43,51</t>
+          <t>-62,72; -44,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 93,47</t>
+          <t>-49,62; -32,21</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-13,68</t>
+          <t>-13,65</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-16,57</t>
+          <t>-16,63</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-15,75</t>
+          <t>-15,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-19,51; -3,11</t>
+          <t>-19,6; -2,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -12,48</t>
+          <t>-26,3; -11,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -6,15</t>
+          <t>-21,55; -6,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -8,16</t>
+          <t>-24,59; -9,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-40,83; -26,44</t>
+          <t>-41,07; -26,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-23,27; -9,71</t>
+          <t>-23,38; -11,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -9,26</t>
+          <t>-20,88; -8,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-33,28; -22,84</t>
+          <t>-33,31; -22,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -10,46</t>
+          <t>-21,29; -10,93</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-39,53%</t>
+          <t>-39,42%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-27,89%</t>
+          <t>-27,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-31,59%</t>
+          <t>-31,69%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,75; -11,04</t>
+          <t>-50,26; -9,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,18; -37,92</t>
+          <t>-67,7; -39,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-52,82; -19,65</t>
+          <t>-53,88; -22,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-37,93; -15,06</t>
+          <t>-39,27; -16,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-64,93; -47,82</t>
+          <t>-65,26; -46,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,59; -18,1</t>
+          <t>-36,06; -19,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -20,01</t>
+          <t>-39,53; -18,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,76; -48,99</t>
+          <t>-64,0; -47,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -22,24</t>
+          <t>-39,64; -23,5</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>-3,27</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,94</t>
+          <t>-3,21; -0,77</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -2,48</t>
+          <t>-4,76; -2,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,98</t>
+          <t>-3,09; -0,86</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -3,59</t>
+          <t>-6,89; -3,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -6,5</t>
+          <t>-10,08; -6,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 18,52</t>
+          <t>-4,93; -1,73</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -2,52</t>
+          <t>-4,73; -2,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -5,01</t>
+          <t>-6,93; -4,98</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 10,99</t>
+          <t>-3,61; -1,63</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-30,36%</t>
+          <t>-27,25%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>-18,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-1,99%</t>
+          <t>-20,59%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -13,97</t>
+          <t>-41,1; -12,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-59,58; -38,43</t>
+          <t>-60,02; -39,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -14,87</t>
+          <t>-39,56; -13,39</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-37,61; -21,33</t>
+          <t>-36,84; -20,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-53,52; -39,36</t>
+          <t>-53,63; -39,71</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 103,97</t>
+          <t>-26,34; -10,26</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -20,82</t>
+          <t>-36,46; -21,67</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-53,21; -41,94</t>
+          <t>-52,94; -41,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 87,72</t>
+          <t>-27,49; -13,63</t>
         </is>
       </c>
     </row>
